--- a/results/yearly_summaries_averaged_by_run_067.xlsx
+++ b/results/yearly_summaries_averaged_by_run_067.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1_2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="43">
   <si>
     <t xml:space="preserve">run_name</t>
   </si>
@@ -110,6 +111,45 @@
   </si>
   <si>
     <t xml:space="preserve">run_g9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Years w/Events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N. Fishermen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWH Threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg. N. Events per Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg. Obs. Event Duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg. Simulated Events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P99 Simulated Events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observed Losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg. Simulated Losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P99 Simulated Losses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimated Emergency Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total/Average</t>
   </si>
 </sst>
 </file>
@@ -154,15 +194,21 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -181,6 +227,13 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
@@ -210,52 +263,136 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -451,1908 +588,2892 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="6.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="16.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="2" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="22.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="2" width="12.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="10.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="12.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="15.64"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="18" style="2" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="19" style="2" width="15.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="2" width="14.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="14.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="19.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="13.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="6.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="16.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="3" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="22.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="3" width="12.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="10.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="2" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="2" width="15.64"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="18" style="3" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="19" style="3" width="15.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="3" width="14.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="2" width="14.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="19.74"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="2" t="n">
         <v>3290</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>1.65</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>13.7142857142857</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="3" t="n">
         <v>4.90236094437775</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>28.7421428571429</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="3" t="n">
         <v>35.43</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="3" t="n">
         <v>7.55887611749681</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="3" t="n">
         <v>10.3778219522839</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="3" t="n">
         <v>31.2914400760304</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="M2" s="2" t="n">
         <v>2645160</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="N2" s="2" t="n">
         <v>5644972.59885962</v>
       </c>
-      <c r="O2" s="1" t="n">
+      <c r="O2" s="2" t="n">
         <v>17036184</v>
       </c>
-      <c r="P2" s="1" t="n">
+      <c r="P2" s="2" t="n">
         <v>3782131.64123595</v>
       </c>
-      <c r="Q2" s="1" t="n">
+      <c r="Q2" s="2" t="n">
         <v>11414243.28</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="R2" s="3" t="n">
         <v>11.5714285714286</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="S2" s="3" t="n">
         <v>2.14285714285714</v>
       </c>
-      <c r="T2" s="7" t="n">
+      <c r="T2" s="8" t="n">
         <f aca="false">R2/F2</f>
-        <v>0.84375</v>
-      </c>
-      <c r="U2" s="1" t="n">
+        <v>0.843750000000003</v>
+      </c>
+      <c r="U2" s="2" t="n">
         <v>344040</v>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" s="3" t="n">
         <f aca="false">P2/M2</f>
         <v>1.4298309520921</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="2" t="n">
         <v>14424</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>2.66666666666667</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="3" t="n">
         <v>3.83333333333333</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>20.0833333333333</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="3" t="n">
         <v>5.26947884416925</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="3" t="n">
         <v>6.74100281844331</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="3" t="n">
         <v>17.1769444444444</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="M3" s="2" t="n">
         <v>1730880</v>
       </c>
-      <c r="N3" s="1" t="n">
+      <c r="N3" s="2" t="n">
         <v>3007055.68731356</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="O3" s="2" t="n">
         <v>7379318.4</v>
       </c>
-      <c r="P3" s="1" t="n">
+      <c r="P3" s="2" t="n">
         <v>2014727.31050008</v>
       </c>
-      <c r="Q3" s="1" t="n">
+      <c r="Q3" s="2" t="n">
         <v>4944143.328</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="R3" s="3" t="n">
         <v>1.33333333333333</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="S3" s="3" t="n">
         <v>1.33333333333333</v>
       </c>
-      <c r="T3" s="7" t="n">
+      <c r="T3" s="8" t="n">
         <f aca="false">R3/F3</f>
-        <v>0.5</v>
-      </c>
-      <c r="U3" s="1" t="n">
+        <v>0.499999999999998</v>
+      </c>
+      <c r="U3" s="2" t="n">
         <v>865440</v>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="V3" s="3" t="n">
         <f aca="false">P3/M3</f>
         <v>1.16399017291787</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="2" t="n">
         <v>5236</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>1.65</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>9.42857142857143</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <v>4.43873626373626</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>16.543</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="3" t="n">
         <v>9.69304721888756</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="3" t="n">
         <v>14.4730180969724</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="3" t="n">
         <v>44.4750941915228</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="M4" s="2" t="n">
         <v>2719728</v>
       </c>
-      <c r="N4" s="1" t="n">
+      <c r="N4" s="2" t="n">
         <v>7495284.16280466</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="O4" s="2" t="n">
         <v>23171813.28</v>
       </c>
-      <c r="P4" s="1" t="n">
+      <c r="P4" s="2" t="n">
         <v>5021840.38907912</v>
       </c>
-      <c r="Q4" s="1" t="n">
+      <c r="Q4" s="2" t="n">
         <v>15525114.8976</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="R4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="S4" s="3" t="n">
         <v>2.42857142857143</v>
       </c>
-      <c r="T4" s="7" t="n">
+      <c r="T4" s="8" t="n">
         <f aca="false">R4/F4</f>
         <v>0.742424242424242</v>
       </c>
-      <c r="U4" s="1" t="n">
+      <c r="U4" s="2" t="n">
         <v>547536</v>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" s="3" t="n">
         <f aca="false">P4/M4</f>
-        <v>1.84644949387554</v>
+        <v>1.84644949387553</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="2" t="n">
         <v>3853</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>1.75</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>4.17920634920635</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="3" t="n">
         <v>23.1014</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="3" t="n">
         <v>6.79743547832793</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="3" t="n">
         <v>8.86752270452488</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="3" t="n">
         <v>24.9577904761905</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="M5" s="2" t="n">
         <v>1276113.6</v>
       </c>
-      <c r="N5" s="1" t="n">
+      <c r="N5" s="2" t="n">
         <v>2603950.87298727</v>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="O5" s="2" t="n">
         <v>7325909.256</v>
       </c>
-      <c r="P5" s="1" t="n">
+      <c r="P5" s="2" t="n">
         <v>1744647.08490147</v>
       </c>
-      <c r="Q5" s="1" t="n">
+      <c r="Q5" s="2" t="n">
         <v>4908359.20152</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="R5" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="S5" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="T5" s="7" t="n">
+      <c r="T5" s="8" t="n">
         <f aca="false">R5/F5</f>
         <v>0.75</v>
       </c>
-      <c r="U5" s="1" t="n">
+      <c r="U5" s="2" t="n">
         <v>240427.2</v>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="V5" s="3" t="n">
         <f aca="false">P5/M5</f>
         <v>1.36715656419732</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="2" t="n">
         <v>2827</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>4.85714285714286</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>8.45238095238095</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="3" t="n">
         <v>26.4864285714286</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="3" t="n">
         <v>7.70049001888768</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K6" s="3" t="n">
         <v>10.7168833153792</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="L6" s="3" t="n">
         <v>27.5769047619048</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="M6" s="2" t="n">
         <v>959564.571428572</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="N6" s="2" t="n">
         <v>1622336.62670312</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="O6" s="2" t="n">
         <v>4376389.85142857</v>
       </c>
-      <c r="P6" s="1" t="n">
+      <c r="P6" s="2" t="n">
         <v>1086965.53989109</v>
       </c>
-      <c r="Q6" s="1" t="n">
+      <c r="Q6" s="2" t="n">
         <v>2932181.20045714</v>
       </c>
-      <c r="R6" s="2" t="n">
+      <c r="R6" s="3" t="n">
         <v>2.71428571428571</v>
       </c>
-      <c r="S6" s="2" t="n">
+      <c r="S6" s="3" t="n">
         <v>2.14285714285714</v>
       </c>
-      <c r="T6" s="7" t="n">
+      <c r="T6" s="8" t="n">
         <f aca="false">R6/F6</f>
-        <v>0.558823529411765</v>
-      </c>
-      <c r="U6" s="1" t="n">
+        <v>0.558823529411764</v>
+      </c>
+      <c r="U6" s="2" t="n">
         <v>557322.857142857</v>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="V6" s="3" t="n">
         <f aca="false">P6/M6</f>
         <v>1.13276956262865</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="2" t="n">
         <v>4606</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1" t="n">
         <v>1.25</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>6.83333333333333</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>4.50653594771242</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="3" t="n">
         <v>24.2403333333333</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="3" t="n">
         <v>6.29072331050592</v>
       </c>
-      <c r="K7" s="2" t="n">
+      <c r="K7" s="3" t="n">
         <v>7.67818173482392</v>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="L7" s="3" t="n">
         <v>21.3267973856209</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="M7" s="2" t="n">
         <v>1851612</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="N7" s="2" t="n">
         <v>2964151.48683472</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="O7" s="2" t="n">
         <v>8136038.4</v>
       </c>
-      <c r="P7" s="1" t="n">
+      <c r="P7" s="2" t="n">
         <v>1985981.49617927</v>
       </c>
-      <c r="Q7" s="1" t="n">
+      <c r="Q7" s="2" t="n">
         <v>5451145.728</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="R7" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="S7" s="2" t="n">
+      <c r="S7" s="3" t="n">
         <v>2.33333333333333</v>
       </c>
-      <c r="T7" s="7" t="n">
+      <c r="T7" s="8" t="n">
         <f aca="false">R7/F7</f>
         <v>0.658536585365854</v>
       </c>
-      <c r="U7" s="1" t="n">
+      <c r="U7" s="2" t="n">
         <v>515872</v>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="V7" s="3" t="n">
         <f aca="false">P7/M7</f>
         <v>1.07256892706424</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="2" t="n">
         <v>3948</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>1.8</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>13.4285714285714</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <v>4.84617925933716</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="3" t="n">
         <v>26.088</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" s="3" t="n">
         <v>7.01572092020368</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K8" s="3" t="n">
         <v>9.50310507894566</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L8" s="3" t="n">
         <v>28.1042308549846</v>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="M8" s="2" t="n">
         <v>3086208</v>
       </c>
-      <c r="N8" s="1" t="n">
+      <c r="N8" s="2" t="n">
         <v>6057500.96786779</v>
       </c>
-      <c r="O8" s="1" t="n">
+      <c r="O8" s="2" t="n">
         <v>17980207.2</v>
       </c>
-      <c r="P8" s="1" t="n">
+      <c r="P8" s="2" t="n">
         <v>4058525.64847142</v>
       </c>
-      <c r="Q8" s="1" t="n">
+      <c r="Q8" s="2" t="n">
         <v>12046738.824</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R8" s="3" t="n">
         <v>11.1428571428571</v>
       </c>
-      <c r="S8" s="2" t="n">
+      <c r="S8" s="3" t="n">
         <v>2.28571428571429</v>
       </c>
-      <c r="T8" s="7" t="n">
+      <c r="T8" s="8" t="n">
         <f aca="false">R8/F8</f>
-        <v>0.829787234042553</v>
-      </c>
-      <c r="U8" s="1" t="n">
+        <v>0.829787234042552</v>
+      </c>
+      <c r="U8" s="2" t="n">
         <v>385776</v>
       </c>
-      <c r="V8" s="2" t="n">
+      <c r="V8" s="3" t="n">
         <f aca="false">P8/M8</f>
         <v>1.31505253322894</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="10" t="n">
         <v>3290</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="9" t="n">
         <v>1.65</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="11" t="n">
         <v>10.5714285714286</v>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="11" t="n">
         <v>4.73537414965986</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H9" s="11" t="n">
         <v>27.5068571428571</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I9" s="11" t="n">
         <v>34.1428571428572</v>
       </c>
-      <c r="J9" s="10" t="n">
+      <c r="J9" s="11" t="n">
         <v>7.35289720524353</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K9" s="11" t="n">
         <v>10.7480088082854</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L9" s="11" t="n">
         <v>33.0694563492064</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="10" t="n">
         <v>1985280</v>
       </c>
-      <c r="N9" s="9" t="n">
+      <c r="N9" s="10" t="n">
         <v>4441075.95917939</v>
       </c>
-      <c r="O9" s="9" t="n">
+      <c r="O9" s="10" t="n">
         <v>13623081.6</v>
       </c>
-      <c r="P9" s="9" t="n">
+      <c r="P9" s="10" t="n">
         <v>2975520.89265019</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="10" t="n">
         <v>9127464.672</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="R9" s="11" t="n">
         <v>9.42857142857143</v>
       </c>
-      <c r="S9" s="10" t="n">
+      <c r="S9" s="11" t="n">
         <v>1.14285714285714</v>
       </c>
-      <c r="T9" s="11" t="n">
+      <c r="T9" s="12" t="n">
         <f aca="false">R9/F9</f>
-        <v>0.891891891891892</v>
-      </c>
-      <c r="U9" s="9" t="n">
+        <v>0.89189189189189</v>
+      </c>
+      <c r="U9" s="10" t="n">
         <v>141000</v>
       </c>
-      <c r="V9" s="10" t="n">
+      <c r="V9" s="11" t="n">
         <f aca="false">P9/M9</f>
         <v>1.49879155214891</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="2" t="n">
         <f aca="false">SUM(D2:D9)</f>
         <v>41474</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <f aca="false">AVERAGE(F2:F9)</f>
         <v>8.4875</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <f aca="false">AVERAGE(G2:G9)</f>
         <v>4.98676339996801</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="3" t="n">
         <f aca="false">AVERAGE(H2:H9)</f>
         <v>24.0989369047619</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="3" t="n">
         <f aca="false">AVERAGE(I2:I9)</f>
-        <v>30.9466071428571</v>
-      </c>
-      <c r="J10" s="2" t="n">
+        <v>30.9466071428572</v>
+      </c>
+      <c r="J10" s="3" t="n">
         <f aca="false">AVERAGE(J2:J9)</f>
-        <v>7.20983363921529</v>
-      </c>
-      <c r="K10" s="2" t="n">
+        <v>7.2098336392153</v>
+      </c>
+      <c r="K10" s="3" t="n">
         <f aca="false">AVERAGE(K2:K9)</f>
-        <v>9.88819306370734</v>
-      </c>
-      <c r="L10" s="2" t="n">
+        <v>9.88819306370733</v>
+      </c>
+      <c r="L10" s="3" t="n">
         <f aca="false">AVERAGE(L2:L9)</f>
         <v>28.4973323174881</v>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="M10" s="2" t="n">
         <f aca="false">SUM(M2:M9)</f>
         <v>16254546.1714286</v>
       </c>
-      <c r="N10" s="1" t="n">
+      <c r="N10" s="2" t="n">
         <f aca="false">SUM(N2:N9)</f>
         <v>33836328.3625501</v>
       </c>
-      <c r="O10" s="1" t="n">
+      <c r="O10" s="2" t="n">
         <f aca="false">SUM(O2:O9)</f>
         <v>99028941.9874286</v>
       </c>
-      <c r="P10" s="1" t="n">
+      <c r="P10" s="2" t="n">
         <f aca="false">SUM(P2:P9)</f>
         <v>22670340.0029086</v>
       </c>
-      <c r="Q10" s="1" t="n">
+      <c r="Q10" s="2" t="n">
         <f aca="false">SUM(Q2:Q9)</f>
         <v>66349391.1315771</v>
       </c>
-      <c r="R10" s="0"/>
-      <c r="T10" s="7" t="n">
+      <c r="R10" s="1"/>
+      <c r="T10" s="8" t="n">
         <f aca="false">AVERAGE(T2:T9)</f>
         <v>0.721901685392038</v>
       </c>
-      <c r="U10" s="1" t="n">
+      <c r="U10" s="2" t="n">
         <f aca="false">SUM(U2:U9)</f>
         <v>3597414.05714286</v>
       </c>
-      <c r="V10" s="2" t="n">
+      <c r="V10" s="3" t="n">
         <f aca="false">P10/M10</f>
         <v>1.39470765678819</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D12" s="2" t="n">
         <v>3290</v>
       </c>
-      <c r="E12" s="0" t="n">
+      <c r="E12" s="1" t="n">
         <v>1.65</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="3" t="n">
         <v>7.10515873015873</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="3" t="n">
         <v>17.7985714285714</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="3" t="n">
         <v>23.2857142857143</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J12" s="3" t="n">
         <v>9.49675575972016</v>
       </c>
-      <c r="K12" s="2" t="n">
+      <c r="K12" s="3" t="n">
         <v>12.3970069314535</v>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="L12" s="3" t="n">
         <v>34.9246825396825</v>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="M12" s="2" t="n">
         <v>1646880</v>
       </c>
-      <c r="N12" s="1" t="n">
+      <c r="N12" s="2" t="n">
         <v>2928371.66243788</v>
       </c>
-      <c r="O12" s="1" t="n">
+      <c r="O12" s="2" t="n">
         <v>8246920.8</v>
       </c>
-      <c r="P12" s="1" t="n">
+      <c r="P12" s="2" t="n">
         <v>1962009.01383338</v>
       </c>
-      <c r="Q12" s="1" t="n">
+      <c r="Q12" s="2" t="n">
         <v>5525436.936</v>
       </c>
-      <c r="R12" s="2" t="n">
+      <c r="R12" s="3" t="n">
         <v>5.57142857142857</v>
       </c>
-      <c r="S12" s="2" t="n">
+      <c r="S12" s="3" t="n">
         <v>0.428571428571429</v>
       </c>
-      <c r="T12" s="7" t="n">
+      <c r="T12" s="8" t="n">
         <f aca="false">R12/F12</f>
-        <v>0.928571428571429</v>
-      </c>
-      <c r="U12" s="1" t="n">
+        <v>0.928571428571428</v>
+      </c>
+      <c r="U12" s="2" t="n">
         <v>157920</v>
       </c>
-      <c r="V12" s="2" t="n">
+      <c r="V12" s="3" t="n">
         <f aca="false">P12/M12</f>
         <v>1.19134910487308</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D13" s="2" t="n">
         <v>14424</v>
       </c>
-      <c r="E13" s="0" t="n">
+      <c r="E13" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="3" t="n">
         <v>9.07</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I13" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" s="3" t="n">
         <v>6.68095238095238</v>
       </c>
-      <c r="K13" s="2" t="n">
+      <c r="K13" s="3" t="n">
         <v>7.4702380952381</v>
       </c>
-      <c r="L13" s="2" t="n">
+      <c r="L13" s="3" t="n">
         <v>14.73</v>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="M13" s="2" t="n">
         <v>951984</v>
       </c>
-      <c r="N13" s="1" t="n">
+      <c r="N13" s="2" t="n">
         <v>1293008.57142857</v>
       </c>
-      <c r="O13" s="1" t="n">
+      <c r="O13" s="2" t="n">
         <v>2549586.24</v>
       </c>
-      <c r="P13" s="1" t="n">
+      <c r="P13" s="2" t="n">
         <v>866315.742857143</v>
       </c>
-      <c r="Q13" s="1" t="n">
+      <c r="Q13" s="2" t="n">
         <v>1708222.7808</v>
       </c>
-      <c r="R13" s="2" t="n">
+      <c r="R13" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="S13" s="2" t="n">
+      <c r="S13" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="T13" s="7" t="n">
+      <c r="T13" s="8" t="n">
         <f aca="false">R13/F13</f>
         <v>0.5</v>
       </c>
-      <c r="U13" s="1" t="n">
+      <c r="U13" s="2" t="n">
         <v>519264</v>
       </c>
-      <c r="V13" s="2" t="n">
+      <c r="V13" s="3" t="n">
         <f aca="false">P13/M13</f>
         <v>0.910010822510823</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D14" s="2" t="n">
         <v>5236</v>
       </c>
-      <c r="E14" s="0" t="n">
+      <c r="E14" s="1" t="n">
         <v>1.65</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="3" t="n">
         <v>4.16666666666667</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G14" s="3" t="n">
         <v>6.28055555555556</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="3" t="n">
         <v>10.74</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" s="3" t="n">
         <v>15.01</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" s="3" t="n">
         <v>13.6363636363636</v>
       </c>
-      <c r="K14" s="2" t="n">
+      <c r="K14" s="3" t="n">
         <v>16.1161156256497</v>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="L14" s="3" t="n">
         <v>47.7901388888889</v>
       </c>
-      <c r="M14" s="1" t="n">
+      <c r="M14" s="2" t="n">
         <v>1717408</v>
       </c>
-      <c r="N14" s="1" t="n">
+      <c r="N14" s="2" t="n">
         <v>3884871.33360047</v>
       </c>
-      <c r="O14" s="1" t="n">
+      <c r="O14" s="2" t="n">
         <v>11341280.72</v>
       </c>
-      <c r="P14" s="1" t="n">
+      <c r="P14" s="2" t="n">
         <v>2602863.79351232</v>
       </c>
-      <c r="Q14" s="1" t="n">
+      <c r="Q14" s="2" t="n">
         <v>7598658.0824</v>
       </c>
-      <c r="R14" s="2" t="n">
+      <c r="R14" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="S14" s="2" t="n">
+      <c r="S14" s="3" t="n">
         <v>1.16666666666667</v>
       </c>
-      <c r="T14" s="7" t="n">
+      <c r="T14" s="8" t="n">
         <f aca="false">R14/F14</f>
         <v>0.72</v>
       </c>
-      <c r="U14" s="1" t="n">
+      <c r="U14" s="2" t="n">
         <v>408408</v>
       </c>
-      <c r="V14" s="2" t="n">
+      <c r="V14" s="3" t="n">
         <f aca="false">P14/M14</f>
         <v>1.51557684226015</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D15" s="2" t="n">
         <v>3853</v>
       </c>
-      <c r="E15" s="0" t="n">
+      <c r="E15" s="1" t="n">
         <v>1.75</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G15" s="3" t="n">
         <v>5.83333333333333</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H15" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="I15" s="3" t="n">
         <v>17.01</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" s="3" t="n">
         <v>8.65369318181818</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K15" s="3" t="n">
         <v>10.3753946737432</v>
       </c>
-      <c r="L15" s="2" t="n">
+      <c r="L15" s="3" t="n">
         <v>26.97425</v>
       </c>
-      <c r="M15" s="1" t="n">
+      <c r="M15" s="2" t="n">
         <v>774453</v>
       </c>
-      <c r="N15" s="1" t="n">
+      <c r="N15" s="2" t="n">
         <v>1325222.40629601</v>
       </c>
-      <c r="O15" s="1" t="n">
+      <c r="O15" s="2" t="n">
         <v>3476022.48</v>
       </c>
-      <c r="P15" s="1" t="n">
+      <c r="P15" s="2" t="n">
         <v>887899.012218327</v>
       </c>
-      <c r="Q15" s="1" t="n">
+      <c r="Q15" s="2" t="n">
         <v>2328935.0616</v>
       </c>
-      <c r="R15" s="2" t="n">
+      <c r="R15" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="S15" s="2" t="n">
+      <c r="S15" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="T15" s="7" t="n">
+      <c r="T15" s="8" t="n">
         <f aca="false">R15/F15</f>
         <v>0.818181818181818</v>
       </c>
-      <c r="U15" s="1" t="n">
+      <c r="U15" s="2" t="n">
         <v>115590</v>
       </c>
-      <c r="V15" s="2" t="n">
+      <c r="V15" s="3" t="n">
         <f aca="false">P15/M15</f>
         <v>1.14648534154859</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D16" s="2" t="n">
         <v>2827</v>
       </c>
-      <c r="E16" s="0" t="n">
+      <c r="E16" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="3" t="n">
         <v>1.71428571428571</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G16" s="3" t="n">
         <v>10.3095238095238</v>
       </c>
-      <c r="H16" s="2" t="n">
+      <c r="H16" s="3" t="n">
         <v>15.6154285714286</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="I16" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" s="3" t="n">
         <v>10.4355348549676</v>
       </c>
-      <c r="K16" s="2" t="n">
+      <c r="K16" s="3" t="n">
         <v>10.4161569976851</v>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="L16" s="3" t="n">
         <v>24.265</v>
       </c>
-      <c r="M16" s="1" t="n">
+      <c r="M16" s="2" t="n">
         <v>600939.428571429</v>
       </c>
-      <c r="N16" s="1" t="n">
+      <c r="N16" s="2" t="n">
         <v>620856.320043719</v>
       </c>
-      <c r="O16" s="1" t="n">
+      <c r="O16" s="2" t="n">
         <v>1473900.87428571</v>
       </c>
-      <c r="P16" s="1" t="n">
+      <c r="P16" s="2" t="n">
         <v>415973.734429292</v>
       </c>
-      <c r="Q16" s="1" t="n">
+      <c r="Q16" s="2" t="n">
         <v>987513.585771429</v>
       </c>
-      <c r="R16" s="2" t="n">
+      <c r="R16" s="3" t="n">
         <v>0.714285714285714</v>
       </c>
-      <c r="S16" s="2" t="n">
+      <c r="S16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="T16" s="7" t="n">
+      <c r="T16" s="8" t="n">
         <f aca="false">R16/F16</f>
-        <v>0.416666666666667</v>
-      </c>
-      <c r="U16" s="1" t="n">
+        <v>0.416666666666668</v>
+      </c>
+      <c r="U16" s="2" t="n">
         <v>421626.857142857</v>
       </c>
-      <c r="V16" s="2" t="n">
+      <c r="V16" s="3" t="n">
         <f aca="false">P16/M16</f>
-        <v>0.692205760933606</v>
+        <v>0.692205760933605</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D17" s="2" t="n">
         <v>4606</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <v>1.25</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G17" s="3" t="n">
         <v>6.33630952380952</v>
       </c>
-      <c r="H17" s="2" t="n">
+      <c r="H17" s="3" t="n">
         <v>12.42425</v>
       </c>
-      <c r="I17" s="2" t="n">
+      <c r="I17" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J17" s="3" t="n">
         <v>8.08718487394958</v>
       </c>
-      <c r="K17" s="2" t="n">
+      <c r="K17" s="3" t="n">
         <v>9.76385473286873</v>
       </c>
-      <c r="L17" s="2" t="n">
+      <c r="L17" s="3" t="n">
         <v>23.8155952380952</v>
       </c>
-      <c r="M17" s="1" t="n">
+      <c r="M17" s="2" t="n">
         <v>1658160</v>
       </c>
-      <c r="N17" s="1" t="n">
+      <c r="N17" s="2" t="n">
         <v>2247861.99890737</v>
       </c>
-      <c r="O17" s="1" t="n">
+      <c r="O17" s="2" t="n">
         <v>5499564</v>
       </c>
-      <c r="P17" s="1" t="n">
+      <c r="P17" s="2" t="n">
         <v>1506067.53926794</v>
       </c>
-      <c r="Q17" s="1" t="n">
+      <c r="Q17" s="2" t="n">
         <v>3684707.88</v>
       </c>
-      <c r="R17" s="2" t="n">
+      <c r="R17" s="3" t="n">
         <v>1.75</v>
       </c>
-      <c r="S17" s="2" t="n">
+      <c r="S17" s="3" t="n">
         <v>2.75</v>
       </c>
-      <c r="T17" s="7" t="n">
+      <c r="T17" s="8" t="n">
         <f aca="false">R17/F17</f>
         <v>0.388888888888889</v>
       </c>
-      <c r="U17" s="1" t="n">
+      <c r="U17" s="2" t="n">
         <v>981078</v>
       </c>
-      <c r="V17" s="2" t="n">
+      <c r="V17" s="3" t="n">
         <f aca="false">P17/M17</f>
         <v>0.908276366133509</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D18" s="2" t="n">
         <v>3948</v>
       </c>
-      <c r="E18" s="0" t="n">
+      <c r="E18" s="1" t="n">
         <v>1.8</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="3" t="n">
         <v>6.14285714285714</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G18" s="3" t="n">
         <v>6.68945578231293</v>
       </c>
-      <c r="H18" s="2" t="n">
+      <c r="H18" s="3" t="n">
         <v>14.8822857142857</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I18" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="J18" s="3" t="n">
         <v>9.33709445316588</v>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>11.5748780802174</v>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="L18" s="3" t="n">
         <v>31.8861780045351</v>
       </c>
-      <c r="M18" s="1" t="n">
+      <c r="M18" s="2" t="n">
         <v>1928880</v>
       </c>
-      <c r="N18" s="1" t="n">
+      <c r="N18" s="2" t="n">
         <v>3351679.48478245</v>
       </c>
-      <c r="O18" s="1" t="n">
+      <c r="O18" s="2" t="n">
         <v>9260519.04</v>
       </c>
-      <c r="P18" s="1" t="n">
+      <c r="P18" s="2" t="n">
         <v>2245625.25480424</v>
       </c>
-      <c r="Q18" s="1" t="n">
+      <c r="Q18" s="2" t="n">
         <v>6204547.7568</v>
       </c>
-      <c r="R18" s="2" t="n">
+      <c r="R18" s="3" t="n">
         <v>5.28571428571429</v>
       </c>
-      <c r="S18" s="2" t="n">
+      <c r="S18" s="3" t="n">
         <v>0.857142857142857</v>
       </c>
-      <c r="T18" s="7" t="n">
+      <c r="T18" s="8" t="n">
         <f aca="false">R18/F18</f>
-        <v>0.86046511627907</v>
-      </c>
-      <c r="U18" s="1" t="n">
+        <v>0.860465116279071</v>
+      </c>
+      <c r="U18" s="2" t="n">
         <v>209808</v>
       </c>
-      <c r="V18" s="2" t="n">
+      <c r="V18" s="3" t="n">
         <f aca="false">P18/M18</f>
         <v>1.16421200634785</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="10" t="n">
         <v>3290</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="9" t="n">
         <v>1.65</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="11" t="n">
         <v>3.85714285714286</v>
       </c>
-      <c r="G19" s="10" t="n">
+      <c r="G19" s="11" t="n">
         <v>7.15952380952381</v>
       </c>
-      <c r="H19" s="10" t="n">
+      <c r="H19" s="11" t="n">
         <v>16.049</v>
       </c>
-      <c r="I19" s="10" t="n">
+      <c r="I19" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="J19" s="10" t="n">
+      <c r="J19" s="11" t="n">
         <v>9.97996698679472</v>
       </c>
-      <c r="K19" s="10" t="n">
+      <c r="K19" s="11" t="n">
         <v>12.9809380134898</v>
       </c>
-      <c r="L19" s="10" t="n">
+      <c r="L19" s="11" t="n">
         <v>37.1659047619048</v>
       </c>
-      <c r="M19" s="9" t="n">
+      <c r="M19" s="10" t="n">
         <v>1116720</v>
       </c>
-      <c r="N19" s="9" t="n">
+      <c r="N19" s="10" t="n">
         <v>1968393.80225913</v>
       </c>
-      <c r="O19" s="9" t="n">
+      <c r="O19" s="10" t="n">
         <v>5623249.2</v>
       </c>
-      <c r="P19" s="9" t="n">
+      <c r="P19" s="10" t="n">
         <v>1318823.84751361</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" s="10" t="n">
         <v>3767576.964</v>
       </c>
-      <c r="R19" s="10" t="n">
+      <c r="R19" s="11" t="n">
         <v>3.71428571428571</v>
       </c>
-      <c r="S19" s="10" t="n">
+      <c r="S19" s="11" t="n">
         <v>0.142857142857143</v>
       </c>
-      <c r="T19" s="11" t="n">
+      <c r="T19" s="12" t="n">
         <f aca="false">R19/F19</f>
-        <v>0.962962962962963</v>
-      </c>
-      <c r="U19" s="9" t="n">
+        <v>0.962962962962961</v>
+      </c>
+      <c r="U19" s="10" t="n">
         <v>33840</v>
       </c>
-      <c r="V19" s="10" t="n">
+      <c r="V19" s="11" t="n">
         <f aca="false">P19/M19</f>
-        <v>1.18097987634646</v>
+        <v>1.18097987634645</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="1" t="n">
+      <c r="D20" s="2" t="n">
         <f aca="false">SUM(D12:D19)</f>
         <v>41474</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="3" t="n">
         <f aca="false">AVERAGE(F12:F19)</f>
         <v>3.76636904761905</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="G20" s="3" t="n">
         <f aca="false">AVERAGE(G12:G19)</f>
         <v>6.90173256802721</v>
       </c>
-      <c r="H20" s="2" t="n">
+      <c r="H20" s="3" t="n">
         <f aca="false">AVERAGE(H12:H19)</f>
         <v>13.6224419642857</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I20" s="3" t="n">
         <f aca="false">AVERAGE(I12:I19)</f>
         <v>18.5382142857143</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J20" s="3" t="n">
         <f aca="false">AVERAGE(J12:J19)</f>
-        <v>9.53844326596652</v>
-      </c>
-      <c r="K20" s="2" t="n">
+        <v>9.53844326596651</v>
+      </c>
+      <c r="K20" s="3" t="n">
         <f aca="false">AVERAGE(K12:K19)</f>
         <v>11.3868228937932</v>
       </c>
-      <c r="L20" s="2" t="n">
+      <c r="L20" s="3" t="n">
         <f aca="false">AVERAGE(L12:L19)</f>
         <v>30.1939686791383</v>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="M20" s="2" t="n">
         <f aca="false">SUM(M12:M19)</f>
         <v>10395424.4285714</v>
       </c>
-      <c r="N20" s="1" t="n">
+      <c r="N20" s="2" t="n">
         <f aca="false">SUM(N12:N19)</f>
         <v>17620265.5797556</v>
       </c>
-      <c r="O20" s="1" t="n">
+      <c r="O20" s="2" t="n">
         <f aca="false">SUM(O12:O19)</f>
         <v>47471043.3542857</v>
       </c>
-      <c r="P20" s="1" t="n">
+      <c r="P20" s="2" t="n">
         <f aca="false">SUM(P12:P19)</f>
         <v>11805577.9384363</v>
       </c>
-      <c r="Q20" s="1" t="n">
+      <c r="Q20" s="2" t="n">
         <f aca="false">SUM(Q12:Q19)</f>
         <v>31805599.0473714</v>
       </c>
-      <c r="R20" s="0"/>
-      <c r="T20" s="7" t="n">
+      <c r="R20" s="1"/>
+      <c r="T20" s="8" t="n">
         <f aca="false">AVERAGE(T12:T19)</f>
         <v>0.699467110193854</v>
       </c>
-      <c r="U20" s="1" t="n">
+      <c r="U20" s="2" t="n">
         <f aca="false">SUM(U12:U19)</f>
         <v>2847534.85714286</v>
       </c>
-      <c r="V20" s="2" t="n">
+      <c r="V20" s="3" t="n">
         <f aca="false">P20/M20</f>
         <v>1.13565136465127</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R21" s="1"/>
+      <c r="T21" s="8"/>
+      <c r="V21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R22" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="S22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="T22" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="U22" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="V22" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C23" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D23" s="2" t="n">
         <v>3290</v>
       </c>
-      <c r="E22" s="0" t="n">
+      <c r="E23" s="1" t="n">
         <v>1.65</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F23" s="3" t="n">
         <v>2.42857142857143</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="G23" s="3" t="n">
         <v>9.20238095238095</v>
       </c>
-      <c r="H22" s="2" t="n">
+      <c r="H23" s="3" t="n">
         <v>10.9645714285714</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="I23" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J23" s="3" t="n">
         <v>12.2816171923315</v>
       </c>
-      <c r="K22" s="2" t="n">
+      <c r="K23" s="3" t="n">
         <v>14.0776968531988</v>
       </c>
-      <c r="L22" s="2" t="n">
+      <c r="L23" s="3" t="n">
         <v>36.1955952380952</v>
       </c>
-      <c r="M22" s="1" t="n">
+      <c r="M23" s="2" t="n">
         <v>891120</v>
       </c>
-      <c r="N22" s="1" t="n">
+      <c r="N23" s="2" t="n">
         <v>1346445.70124541</v>
       </c>
-      <c r="O22" s="1" t="n">
+      <c r="O23" s="2" t="n">
         <v>3459801.6</v>
       </c>
-      <c r="P22" s="1" t="n">
+      <c r="P23" s="2" t="n">
         <v>902118.619834426</v>
       </c>
-      <c r="Q22" s="1" t="n">
+      <c r="Q23" s="2" t="n">
         <v>2318067.072</v>
       </c>
-      <c r="R22" s="2" t="n">
+      <c r="R23" s="3" t="n">
         <v>1.57142857142857</v>
       </c>
-      <c r="S22" s="2" t="n">
+      <c r="S23" s="3" t="n">
         <v>0.857142857142857</v>
       </c>
-      <c r="T22" s="7" t="n">
-        <f aca="false">R22/F22</f>
-        <v>0.647058823529412</v>
-      </c>
-      <c r="U22" s="1" t="n">
+      <c r="T23" s="8" t="n">
+        <f aca="false">R23/F23</f>
+        <v>0.647058823529411</v>
+      </c>
+      <c r="U23" s="2" t="n">
         <v>344040</v>
       </c>
-      <c r="V22" s="2" t="n">
-        <f aca="false">P22/M22</f>
+      <c r="V23" s="3" t="n">
+        <f aca="false">P23/M23</f>
         <v>1.01234246771975</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C24" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D24" s="2" t="n">
         <v>5236</v>
       </c>
-      <c r="E23" s="0" t="n">
+      <c r="E24" s="1" t="n">
         <v>1.65</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F24" s="3" t="n">
         <v>2.25</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="G24" s="3" t="n">
         <v>8.3125</v>
       </c>
-      <c r="H23" s="2" t="n">
+      <c r="H24" s="3" t="n">
         <v>7.688</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="I24" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="J24" s="3" t="n">
         <v>16.7058531746032</v>
       </c>
-      <c r="K23" s="2" t="n">
+      <c r="K24" s="3" t="n">
         <v>19.6074596365064</v>
       </c>
-      <c r="L23" s="2" t="n">
+      <c r="L24" s="3" t="n">
         <v>57.0775</v>
       </c>
-      <c r="M23" s="1" t="n">
+      <c r="M24" s="2" t="n">
         <v>1272348</v>
       </c>
-      <c r="N23" s="1" t="n">
+      <c r="N24" s="2" t="n">
         <v>2695905.27556651</v>
       </c>
-      <c r="O23" s="1" t="n">
+      <c r="O24" s="2" t="n">
         <v>7860754.44</v>
       </c>
-      <c r="P23" s="1" t="n">
+      <c r="P24" s="2" t="n">
         <v>1806256.53462956</v>
       </c>
-      <c r="Q23" s="1" t="n">
+      <c r="Q24" s="2" t="n">
         <v>5266705.4748</v>
       </c>
-      <c r="R23" s="2" t="n">
+      <c r="R24" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="S23" s="2" t="n">
+      <c r="S24" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="T23" s="7" t="n">
-        <f aca="false">R23/F23</f>
+      <c r="T24" s="8" t="n">
+        <f aca="false">R24/F24</f>
         <v>0.888888888888889</v>
       </c>
-      <c r="U23" s="1" t="n">
+      <c r="U24" s="2" t="n">
         <v>125664</v>
       </c>
-      <c r="V23" s="2" t="n">
-        <f aca="false">P23/M23</f>
+      <c r="V24" s="3" t="n">
+        <f aca="false">P24/M24</f>
         <v>1.41962461105732</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C25" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D25" s="2" t="n">
         <v>3853</v>
       </c>
-      <c r="E24" s="0" t="n">
+      <c r="E25" s="1" t="n">
         <v>1.75</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F25" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G25" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="H25" s="3" t="n">
         <v>7.292</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="I25" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="J25" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="K24" s="2" t="n">
+      <c r="K25" s="3" t="n">
         <v>12.4420610339274</v>
       </c>
-      <c r="L24" s="2" t="n">
+      <c r="L25" s="3" t="n">
         <v>30.0425</v>
       </c>
-      <c r="M24" s="1" t="n">
+      <c r="M25" s="2" t="n">
         <v>739776</v>
       </c>
-      <c r="N24" s="1" t="n">
+      <c r="N25" s="2" t="n">
         <v>1150542.26792933</v>
       </c>
-      <c r="O24" s="1" t="n">
+      <c r="O25" s="2" t="n">
         <v>2778090.06</v>
       </c>
-      <c r="P24" s="1" t="n">
+      <c r="P25" s="2" t="n">
         <v>770863.319512651</v>
       </c>
-      <c r="Q24" s="1" t="n">
+      <c r="Q25" s="2" t="n">
         <v>1861320.3402</v>
       </c>
-      <c r="R24" s="2" t="n">
+      <c r="R25" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="S24" s="2" t="n">
+      <c r="S25" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="T24" s="7" t="n">
-        <f aca="false">R24/F24</f>
+      <c r="T25" s="8" t="n">
+        <f aca="false">R25/F25</f>
         <v>1</v>
       </c>
-      <c r="U24" s="1" t="n">
+      <c r="U25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="2" t="n">
-        <f aca="false">P24/M24</f>
+      <c r="V25" s="3" t="n">
+        <f aca="false">P25/M25</f>
         <v>1.04202261159142</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C26" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="1" t="n">
+      <c r="D26" s="2" t="n">
         <v>2827</v>
       </c>
-      <c r="E25" s="0" t="n">
+      <c r="E26" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F26" s="3" t="n">
         <v>1.16666666666667</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G26" s="3" t="n">
         <v>12.3333333333333</v>
       </c>
-      <c r="H25" s="2" t="n">
+      <c r="H26" s="3" t="n">
         <v>10.1201666666667</v>
       </c>
-      <c r="I25" s="2" t="n">
+      <c r="I26" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="J26" s="3" t="n">
         <v>13.2178969178969</v>
       </c>
-      <c r="K25" s="2" t="n">
+      <c r="K26" s="3" t="n">
         <v>10.9983747970934</v>
       </c>
-      <c r="L25" s="2" t="n">
+      <c r="L26" s="3" t="n">
         <v>21.5016666666667</v>
       </c>
-      <c r="M25" s="1" t="n">
+      <c r="M26" s="2" t="n">
         <v>554092</v>
       </c>
-      <c r="N25" s="1" t="n">
+      <c r="N26" s="2" t="n">
         <v>467230.788665208</v>
       </c>
-      <c r="O25" s="1" t="n">
+      <c r="O26" s="2" t="n">
         <v>948006.18</v>
       </c>
-      <c r="P25" s="1" t="n">
+      <c r="P26" s="2" t="n">
         <v>313044.62840569</v>
       </c>
-      <c r="Q25" s="1" t="n">
+      <c r="Q26" s="2" t="n">
         <v>635164.1406</v>
       </c>
-      <c r="R25" s="2" t="n">
+      <c r="R26" s="3" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="S25" s="2" t="n">
+      <c r="S26" s="3" t="n">
         <v>0.833333333333333</v>
       </c>
-      <c r="T25" s="7" t="n">
-        <f aca="false">R25/F25</f>
-        <v>0.285714285714286</v>
-      </c>
-      <c r="U25" s="1" t="n">
+      <c r="T26" s="8" t="n">
+        <f aca="false">R26/F26</f>
+        <v>0.285714285714285</v>
+      </c>
+      <c r="U26" s="2" t="n">
         <v>429704</v>
       </c>
-      <c r="V25" s="2" t="n">
-        <f aca="false">P25/M25</f>
+      <c r="V26" s="3" t="n">
+        <f aca="false">P26/M26</f>
         <v>0.564968684633039</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C27" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="1" t="n">
+      <c r="D27" s="2" t="n">
         <v>4606</v>
       </c>
-      <c r="E26" s="0" t="n">
+      <c r="E27" s="1" t="n">
         <v>1.25</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="F27" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G27" s="3" t="n">
         <v>9.38888888888889</v>
       </c>
-      <c r="H26" s="2" t="n">
+      <c r="H27" s="3" t="n">
         <v>6.947</v>
       </c>
-      <c r="I26" s="2" t="n">
+      <c r="I27" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="J27" s="3" t="n">
         <v>10.8058608058608</v>
       </c>
-      <c r="K26" s="2" t="n">
+      <c r="K27" s="3" t="n">
         <v>12.2143563622154</v>
       </c>
-      <c r="L26" s="2" t="n">
+      <c r="L27" s="3" t="n">
         <v>29.22</v>
       </c>
-      <c r="M26" s="1" t="n">
+      <c r="M27" s="2" t="n">
         <v>1013320</v>
       </c>
-      <c r="N26" s="1" t="n">
+      <c r="N27" s="2" t="n">
         <v>1369939.7174176</v>
       </c>
-      <c r="O26" s="1" t="n">
+      <c r="O27" s="2" t="n">
         <v>3305449.84</v>
       </c>
-      <c r="P26" s="1" t="n">
+      <c r="P27" s="2" t="n">
         <v>917859.610669795</v>
       </c>
-      <c r="Q26" s="1" t="n">
+      <c r="Q27" s="2" t="n">
         <v>2214651.3928</v>
       </c>
-      <c r="R26" s="2" t="n">
+      <c r="R27" s="3" t="n">
         <v>0.666666666666667</v>
       </c>
-      <c r="S26" s="2" t="n">
+      <c r="S27" s="3" t="n">
         <v>1.33333333333333</v>
       </c>
-      <c r="T26" s="7" t="n">
-        <f aca="false">R26/F26</f>
+      <c r="T27" s="8" t="n">
+        <f aca="false">R27/F27</f>
+        <v>0.333333333333334</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>626416</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <f aca="false">P27/M27</f>
+        <v>0.905794428877151</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>3948</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>2.57142857142857</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>9.13014285714286</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>11.0850732600733</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>13.4300371451934</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>34.4439285714286</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>1042272</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>1641906.312793</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>4200829.92</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>1100077.22957131</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>2814556.0464</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>1.71428571428571</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="T28" s="8" t="n">
+        <f aca="false">R28/F28</f>
+        <v>0.666666666666665</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>358704</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <f aca="false">P28/M28</f>
+        <v>1.05546079101358</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>3290</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>10.1628</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>12.7228904428904</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>13.7041688481236</v>
+      </c>
+      <c r="L29" s="11" t="n">
+        <v>36.6593333333334</v>
+      </c>
+      <c r="M29" s="10" t="n">
+        <v>844872</v>
+      </c>
+      <c r="N29" s="10" t="n">
+        <v>1097202.66271793</v>
+      </c>
+      <c r="O29" s="10" t="n">
+        <v>2952946.08</v>
+      </c>
+      <c r="P29" s="10" t="n">
+        <v>735125.784021014</v>
+      </c>
+      <c r="Q29" s="10" t="n">
+        <v>1978473.8736</v>
+      </c>
+      <c r="R29" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S29" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T29" s="12" t="n">
+        <f aca="false">R29/F29</f>
+        <v>0.7</v>
+      </c>
+      <c r="U29" s="10" t="n">
+        <v>205296</v>
+      </c>
+      <c r="V29" s="11" t="n">
+        <f aca="false">P29/M29</f>
+        <v>0.870103144643229</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D30" s="2" t="n">
+        <f aca="false">SUM(D22:D29)</f>
+        <v>27050</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <f aca="false">AVERAGE(F22:F29)</f>
+        <v>2.05952380952381</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <f aca="false">AVERAGE(G22:G29)</f>
+        <v>9.54815759637188</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <f aca="false">AVERAGE(H22:H29)</f>
+        <v>8.90066870748299</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <f aca="false">AVERAGE(I22:I29)</f>
+        <v>13.4285714285714</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <f aca="false">AVERAGE(J22:J29)</f>
+        <v>12.4741702562366</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <f aca="false">AVERAGE(K22:K29)</f>
+        <v>13.7820220966083</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <f aca="false">AVERAGE(L22:L29)</f>
+        <v>35.020074829932</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <f aca="false">SUM(M22:M29)</f>
+        <v>6357800</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <f aca="false">SUM(N22:N29)</f>
+        <v>9769172.72633499</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <f aca="false">SUM(O22:O29)</f>
+        <v>25505878.12</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <f aca="false">SUM(P22:P29)</f>
+        <v>6545345.72664445</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <f aca="false">SUM(Q22:Q29)</f>
+        <v>17088938.3404</v>
+      </c>
+      <c r="R30" s="1"/>
+      <c r="T30" s="8" t="n">
+        <f aca="false">AVERAGE(T22:T29)</f>
+        <v>0.64595171401894</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <f aca="false">SUM(U22:U29)</f>
+        <v>2089824</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <f aca="false">P30/M30</f>
+        <v>1.02949852569198</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B1:W1048576"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="13" width="3.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="11.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="14" width="8.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="11.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="14" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="12.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="16" width="12.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="12.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="10.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="13.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="13.61"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="13" style="16" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="14" style="16" width="15.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="15" width="14.94"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16" style="13" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="13" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="2" s="13" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M3" s="14"/>
+    </row>
+    <row r="4" s="17" customFormat="true" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" s="22" t="n">
+        <v>3290</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>2.42857142857143</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>9.20238095238095</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>10.9645714285714</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>891120</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>902118.619834426</v>
+      </c>
+      <c r="L5" s="15" t="n">
+        <v>2318067.072</v>
+      </c>
+      <c r="M5" s="16" t="n">
+        <v>1.57142857142857</v>
+      </c>
+      <c r="N5" s="16" t="n">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="O5" s="15" t="n">
+        <v>344040</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>5236</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>8.3125</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>7.688</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>1272348</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>1806256.53462956</v>
+      </c>
+      <c r="L6" s="15" t="n">
+        <v>5266705.4748</v>
+      </c>
+      <c r="M6" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O6" s="15" t="n">
+        <v>125664</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>3853</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>7.292</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>739776</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>770863.319512651</v>
+      </c>
+      <c r="L7" s="15" t="n">
+        <v>1861320.3402</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>2827</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>1.16666666666667</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>12.3333333333333</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>10.1201666666667</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>554092</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>313044.62840569</v>
+      </c>
+      <c r="L8" s="15" t="n">
+        <v>635164.1406</v>
+      </c>
+      <c r="M8" s="16" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="U26" s="1" t="n">
+      <c r="N8" s="16" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="O8" s="15" t="n">
+        <v>429704</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>4606</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>9.38888888888889</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>6.947</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>1013320</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>917859.610669795</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>2214651.3928</v>
+      </c>
+      <c r="M9" s="16" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="N9" s="16" t="n">
+        <v>1.33333333333333</v>
+      </c>
+      <c r="O9" s="15" t="n">
         <v>626416</v>
       </c>
-      <c r="V26" s="2" t="n">
-        <f aca="false">P26/M26</f>
-        <v>0.905794428877151</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="0" t="n">
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="D10" s="22" t="n">
+        <v>3948</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>2.57142857142857</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>9.13014285714286</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>1042272</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>1100077.22957131</v>
+      </c>
+      <c r="L10" s="15" t="n">
+        <v>2814556.0464</v>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>1.71428571428571</v>
+      </c>
+      <c r="N10" s="16" t="n">
+        <v>0.857142857142857</v>
+      </c>
+      <c r="O10" s="15" t="n">
+        <v>358704</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="24" t="n">
+        <v>3290</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F11" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H11" s="26" t="n">
+        <v>10.1628</v>
+      </c>
+      <c r="I11" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" s="27" t="n">
+        <v>844872</v>
+      </c>
+      <c r="K11" s="27" t="n">
+        <v>735125.784021014</v>
+      </c>
+      <c r="L11" s="27" t="n">
+        <v>1978473.8736</v>
+      </c>
+      <c r="M11" s="26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N11" s="26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O11" s="27" t="n">
+        <v>205296</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="29" t="n">
+        <f aca="false">SUM(D4:D11)</f>
+        <v>27050</v>
+      </c>
+      <c r="E12" s="30"/>
+      <c r="F12" s="31" t="n">
+        <f aca="false">AVERAGE(F4:F11)</f>
+        <v>2.05952380952381</v>
+      </c>
+      <c r="G12" s="31" t="n">
+        <f aca="false">AVERAGE(G4:G11)</f>
+        <v>9.54815759637188</v>
+      </c>
+      <c r="H12" s="31" t="n">
+        <f aca="false">AVERAGE(H4:H11)</f>
+        <v>8.90066870748299</v>
+      </c>
+      <c r="I12" s="31" t="n">
+        <f aca="false">AVERAGE(I4:I11)</f>
+        <v>13.4285714285714</v>
+      </c>
+      <c r="J12" s="32" t="n">
+        <f aca="false">SUM(J4:J11)</f>
+        <v>6357800</v>
+      </c>
+      <c r="K12" s="32" t="n">
+        <f aca="false">SUM(K4:K11)</f>
+        <v>6545345.72664445</v>
+      </c>
+      <c r="L12" s="32" t="n">
+        <f aca="false">SUM(L4:L11)</f>
+        <v>17088938.3404</v>
+      </c>
+      <c r="M12" s="30"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="32" t="n">
+        <f aca="false">SUM(O4:O11)</f>
+        <v>2089824</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="M16" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="O16" s="19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="D27" s="1" t="n">
+      <c r="D17" s="22" t="n">
+        <v>3290</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>7.10515873015873</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <v>17.7985714285714</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>23.2857142857143</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>1646880</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>1962009.01383338</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>5525436.936</v>
+      </c>
+      <c r="M17" s="15" t="n">
+        <v>1646880</v>
+      </c>
+      <c r="N17" s="15" t="n">
+        <v>2928371.66243788</v>
+      </c>
+      <c r="O17" s="15" t="n">
+        <v>157920</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>14424</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="I18" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="J18" s="15" t="n">
+        <v>951984</v>
+      </c>
+      <c r="K18" s="15" t="n">
+        <v>866315.742857143</v>
+      </c>
+      <c r="L18" s="15" t="n">
+        <v>1708222.7808</v>
+      </c>
+      <c r="M18" s="15" t="n">
+        <v>951984</v>
+      </c>
+      <c r="N18" s="15" t="n">
+        <v>1293008.57142857</v>
+      </c>
+      <c r="O18" s="15" t="n">
+        <v>519264</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>5236</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>4.16666666666667</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>6.28055555555556</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="I19" s="16" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <v>1717408</v>
+      </c>
+      <c r="K19" s="15" t="n">
+        <v>2602863.79351232</v>
+      </c>
+      <c r="L19" s="15" t="n">
+        <v>7598658.0824</v>
+      </c>
+      <c r="M19" s="15" t="n">
+        <v>1717408</v>
+      </c>
+      <c r="N19" s="15" t="n">
+        <v>3884871.33360047</v>
+      </c>
+      <c r="O19" s="15" t="n">
+        <v>408408</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>3853</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>5.83333333333333</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="J20" s="15" t="n">
+        <v>774453</v>
+      </c>
+      <c r="K20" s="15" t="n">
+        <v>887899.012218327</v>
+      </c>
+      <c r="L20" s="15" t="n">
+        <v>2328935.0616</v>
+      </c>
+      <c r="M20" s="15" t="n">
+        <v>774453</v>
+      </c>
+      <c r="N20" s="15" t="n">
+        <v>1325222.40629601</v>
+      </c>
+      <c r="O20" s="15" t="n">
+        <v>115590</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>2827</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>1.71428571428571</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>10.3095238095238</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>15.6154285714286</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="J21" s="15" t="n">
+        <v>600939.428571429</v>
+      </c>
+      <c r="K21" s="15" t="n">
+        <v>415973.734429292</v>
+      </c>
+      <c r="L21" s="15" t="n">
+        <v>987513.585771429</v>
+      </c>
+      <c r="M21" s="15" t="n">
+        <v>600939.428571429</v>
+      </c>
+      <c r="N21" s="15" t="n">
+        <v>620856.320043719</v>
+      </c>
+      <c r="O21" s="15" t="n">
+        <v>421626.857142857</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>4606</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>6.33630952380952</v>
+      </c>
+      <c r="H22" s="16" t="n">
+        <v>12.42425</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="J22" s="15" t="n">
+        <v>1658160</v>
+      </c>
+      <c r="K22" s="15" t="n">
+        <v>1506067.53926794</v>
+      </c>
+      <c r="L22" s="15" t="n">
+        <v>3684707.88</v>
+      </c>
+      <c r="M22" s="15" t="n">
+        <v>1658160</v>
+      </c>
+      <c r="N22" s="15" t="n">
+        <v>2247861.99890737</v>
+      </c>
+      <c r="O22" s="15" t="n">
+        <v>981078</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" s="22" t="n">
         <v>3948</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E23" s="14" t="n">
         <v>1.8</v>
       </c>
-      <c r="F27" s="2" t="n">
-        <v>2.57142857142857</v>
-      </c>
-      <c r="G27" s="2" t="n">
+      <c r="F23" s="16" t="n">
+        <v>6.14285714285714</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>6.68945578231293</v>
+      </c>
+      <c r="H23" s="16" t="n">
+        <v>14.8822857142857</v>
+      </c>
+      <c r="I23" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="J23" s="15" t="n">
+        <v>1928880</v>
+      </c>
+      <c r="K23" s="15" t="n">
+        <v>2245625.25480424</v>
+      </c>
+      <c r="L23" s="15" t="n">
+        <v>6204547.7568</v>
+      </c>
+      <c r="M23" s="15" t="n">
+        <v>1928880</v>
+      </c>
+      <c r="N23" s="15" t="n">
+        <v>3351679.48478245</v>
+      </c>
+      <c r="O23" s="15" t="n">
+        <v>209808</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="H27" s="2" t="n">
-        <v>9.13014285714286</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>11.0850732600733</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>13.4300371451934</v>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>34.4439285714286</v>
-      </c>
-      <c r="M27" s="1" t="n">
-        <v>1042272</v>
-      </c>
-      <c r="N27" s="1" t="n">
-        <v>1641906.312793</v>
-      </c>
-      <c r="O27" s="1" t="n">
-        <v>4200829.92</v>
-      </c>
-      <c r="P27" s="1" t="n">
-        <v>1100077.22957131</v>
-      </c>
-      <c r="Q27" s="1" t="n">
-        <v>2814556.0464</v>
-      </c>
-      <c r="R27" s="2" t="n">
-        <v>1.71428571428571</v>
-      </c>
-      <c r="S27" s="2" t="n">
-        <v>0.857142857142857</v>
-      </c>
-      <c r="T27" s="7" t="n">
-        <f aca="false">R27/F27</f>
-        <v>0.666666666666666</v>
-      </c>
-      <c r="U27" s="1" t="n">
-        <v>358704</v>
-      </c>
-      <c r="V27" s="2" t="n">
-        <f aca="false">P27/M27</f>
-        <v>1.05546079101358</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="8" t="n">
+      <c r="C24" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="C28" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D28" s="9" t="n">
+      <c r="D24" s="24" t="n">
         <v>3290</v>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="E24" s="25" t="n">
         <v>1.65</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" s="10" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H28" s="10" t="n">
-        <v>10.1628</v>
-      </c>
-      <c r="I28" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>12.7228904428904</v>
-      </c>
-      <c r="K28" s="10" t="n">
-        <v>13.7041688481236</v>
-      </c>
-      <c r="L28" s="10" t="n">
-        <v>36.6593333333334</v>
-      </c>
-      <c r="M28" s="9" t="n">
-        <v>844872</v>
-      </c>
-      <c r="N28" s="9" t="n">
-        <v>1097202.66271793</v>
-      </c>
-      <c r="O28" s="9" t="n">
-        <v>2952946.08</v>
-      </c>
-      <c r="P28" s="9" t="n">
-        <v>735125.784021014</v>
-      </c>
-      <c r="Q28" s="9" t="n">
-        <v>1978473.8736</v>
-      </c>
-      <c r="R28" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S28" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T28" s="11" t="n">
-        <f aca="false">R28/F28</f>
-        <v>0.7</v>
-      </c>
-      <c r="U28" s="9" t="n">
-        <v>205296</v>
-      </c>
-      <c r="V28" s="10" t="n">
-        <f aca="false">P28/M28</f>
-        <v>0.870103144643229</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D29" s="1" t="n">
-        <f aca="false">SUM(D21:D28)</f>
-        <v>27050</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <f aca="false">AVERAGE(F21:F28)</f>
-        <v>2.05952380952381</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <f aca="false">AVERAGE(G21:G28)</f>
-        <v>9.54815759637188</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <f aca="false">AVERAGE(H21:H28)</f>
-        <v>8.90066870748299</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <f aca="false">AVERAGE(I21:I28)</f>
-        <v>13.4285714285714</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <f aca="false">AVERAGE(J21:J28)</f>
-        <v>12.4741702562366</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <f aca="false">AVERAGE(K21:K28)</f>
-        <v>13.7820220966083</v>
-      </c>
-      <c r="L29" s="2" t="n">
-        <f aca="false">AVERAGE(L21:L28)</f>
-        <v>35.020074829932</v>
-      </c>
-      <c r="M29" s="1" t="n">
-        <f aca="false">SUM(M21:M28)</f>
-        <v>6357800</v>
-      </c>
-      <c r="N29" s="1" t="n">
-        <f aca="false">SUM(N21:N28)</f>
-        <v>9769172.726335</v>
-      </c>
-      <c r="O29" s="1" t="n">
-        <f aca="false">SUM(O21:O28)</f>
-        <v>25505878.12</v>
-      </c>
-      <c r="P29" s="1" t="n">
-        <f aca="false">SUM(P21:P28)</f>
-        <v>6545345.72664445</v>
-      </c>
-      <c r="Q29" s="1" t="n">
-        <f aca="false">SUM(Q21:Q28)</f>
-        <v>17088938.3404</v>
-      </c>
-      <c r="R29" s="0"/>
-      <c r="T29" s="7" t="n">
-        <f aca="false">AVERAGE(T21:T28)</f>
-        <v>0.645951714018941</v>
-      </c>
-      <c r="U29" s="1" t="n">
-        <f aca="false">SUM(U21:U28)</f>
-        <v>2089824</v>
-      </c>
-      <c r="V29" s="2" t="n">
-        <f aca="false">P29/M29</f>
-        <v>1.02949852569198</v>
-      </c>
-    </row>
+      <c r="F24" s="26" t="n">
+        <v>3.85714285714286</v>
+      </c>
+      <c r="G24" s="26" t="n">
+        <v>7.15952380952381</v>
+      </c>
+      <c r="H24" s="26" t="n">
+        <v>16.049</v>
+      </c>
+      <c r="I24" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="J24" s="27" t="n">
+        <v>1116720</v>
+      </c>
+      <c r="K24" s="27" t="n">
+        <v>1318823.84751361</v>
+      </c>
+      <c r="L24" s="27" t="n">
+        <v>3767576.964</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1116720</v>
+      </c>
+      <c r="N24" s="27" t="n">
+        <v>1968393.80225913</v>
+      </c>
+      <c r="O24" s="27" t="n">
+        <v>33840</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="29" t="n">
+        <f aca="false">SUM(D17:D24)</f>
+        <v>41474</v>
+      </c>
+      <c r="E25" s="30"/>
+      <c r="F25" s="31" t="n">
+        <f aca="false">AVERAGE(F17:F24)</f>
+        <v>3.76636904761905</v>
+      </c>
+      <c r="G25" s="31" t="n">
+        <f aca="false">AVERAGE(G17:G24)</f>
+        <v>6.90173256802721</v>
+      </c>
+      <c r="H25" s="31" t="n">
+        <f aca="false">AVERAGE(H17:H24)</f>
+        <v>13.6224419642857</v>
+      </c>
+      <c r="I25" s="31" t="n">
+        <f aca="false">AVERAGE(I17:I24)</f>
+        <v>18.5382142857143</v>
+      </c>
+      <c r="J25" s="32" t="n">
+        <f aca="false">SUM(J17:J24)</f>
+        <v>10395424.4285714</v>
+      </c>
+      <c r="K25" s="32" t="n">
+        <f aca="false">SUM(K17:K24)</f>
+        <v>11805577.9384363</v>
+      </c>
+      <c r="L25" s="32" t="n">
+        <f aca="false">SUM(L17:L24)</f>
+        <v>31805599.0473714</v>
+      </c>
+      <c r="M25" s="32" t="n">
+        <f aca="false">SUM(M17:M24)</f>
+        <v>10395424.4285714</v>
+      </c>
+      <c r="N25" s="32" t="n">
+        <f aca="false">SUM(N17:N24)</f>
+        <v>17620265.5797556</v>
+      </c>
+      <c r="O25" s="32" t="n">
+        <f aca="false">SUM(O17:O24)</f>
+        <v>2847534.85714286</v>
+      </c>
+    </row>
+    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
